--- a/analysis/tables/gpt-neox-20b.xlsx
+++ b/analysis/tables/gpt-neox-20b.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8560918861505338</v>
+        <v>0.6220934372693879</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.138685940858836</v>
+        <v>-0.04736947300277916</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.856x - 0.139</t>
+          <t>y = 0.622x - 0.047</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.841212927430945</v>
+        <v>0.8412129274309452</v>
       </c>
       <c r="H3" t="n">
         <v>0.07476233464372814</v>
       </c>
       <c r="I3" t="n">
-        <v>0.16199889649982</v>
+        <v>0.07614527041259647</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7174059452916978</v>
+        <v>0.5747239642666088</v>
       </c>
       <c r="K3" t="n">
         <v>0.1757301061537291</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8508086154599527</v>
+        <v>0.620090912117839</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1234640130749899</v>
+        <v>-0.04184108536940623</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.851x - 0.123</t>
+          <t>y = 0.620x - 0.042</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8434796649577093</v>
+        <v>0.8432992926473709</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07467833568148227</v>
+        <v>0.07468501977556347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1451137316095988</v>
+        <v>0.06747572743245583</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7273446023849628</v>
+        <v>0.5782498267484327</v>
       </c>
       <c r="K4" t="n">
         <v>0.1757301061537291</v>
